--- a/output/pca-table.xlsx
+++ b/output/pca-table.xlsx
@@ -383,13 +383,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.06309622596868981</v>
+        <v>-0.06309622596868988</v>
       </c>
       <c r="C2">
-        <v>0.01554393947948385</v>
+        <v>0.01554393947948438</v>
       </c>
       <c r="D2">
-        <v>-0.7904922125385031</v>
+        <v>-0.7904922125384998</v>
       </c>
     </row>
     <row r="3">
@@ -399,13 +399,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1377849933319893</v>
+        <v>0.1377849933319895</v>
       </c>
       <c r="C3">
         <v>0.5066271872347297</v>
       </c>
       <c r="D3">
-        <v>-0.4396845389176793</v>
+        <v>-0.4396845389176809</v>
       </c>
     </row>
     <row r="4">
@@ -415,13 +415,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.2328485767075089</v>
+        <v>-0.2328485767075087</v>
       </c>
       <c r="C4">
-        <v>0.3891164140440386</v>
+        <v>0.389116414044039</v>
       </c>
       <c r="D4">
-        <v>0.003282764992031423</v>
+        <v>0.003282764992030707</v>
       </c>
     </row>
     <row r="5">
@@ -431,13 +431,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.3352869952580392</v>
+        <v>-0.3352869952580391</v>
       </c>
       <c r="C5">
-        <v>0.03403267527426095</v>
+        <v>0.03403267527426156</v>
       </c>
       <c r="D5">
-        <v>-0.2377652749921168</v>
+        <v>-0.2377652749921193</v>
       </c>
     </row>
     <row r="6">
@@ -447,13 +447,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.4498619146107798</v>
+        <v>0.4498619146107802</v>
       </c>
       <c r="C6">
-        <v>0.762373093901752</v>
+        <v>0.7623730939017512</v>
       </c>
       <c r="D6">
-        <v>0.1518297743153331</v>
+        <v>0.1518297743153346</v>
       </c>
     </row>
     <row r="7">
@@ -463,13 +463,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.4902863320470105</v>
+        <v>-0.4902863320470103</v>
       </c>
       <c r="C7">
-        <v>0.1962117374198918</v>
+        <v>0.1962117374198926</v>
       </c>
       <c r="D7">
-        <v>-0.2965964269157673</v>
+        <v>-0.2965964269157695</v>
       </c>
     </row>
     <row r="8">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.6988151458067138</v>
+        <v>0.6988151458067139</v>
       </c>
       <c r="C8">
-        <v>0.4459562474045553</v>
+        <v>0.4459562474045543</v>
       </c>
       <c r="D8">
-        <v>-0.02812532558616212</v>
+        <v>-0.02812532558616221</v>
       </c>
     </row>
     <row r="9">
@@ -495,13 +495,13 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.7415899166677825</v>
+        <v>-0.7415899166677822</v>
       </c>
       <c r="C9">
-        <v>0.6156900457253118</v>
+        <v>0.6156900457253127</v>
       </c>
       <c r="D9">
-        <v>0.1510981014405888</v>
+        <v>0.1510981014405899</v>
       </c>
     </row>
     <row r="10">
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.7815495460260581</v>
+        <v>-0.7815495460260582</v>
       </c>
       <c r="C10">
-        <v>-0.3747626912863143</v>
+        <v>-0.3747626912863133</v>
       </c>
       <c r="D10">
-        <v>-0.07938292856814384</v>
+        <v>-0.07938292856814468</v>
       </c>
     </row>
     <row r="11">
@@ -527,13 +527,13 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.8421734367312055</v>
+        <v>-0.8421734367312054</v>
       </c>
       <c r="C11">
-        <v>0.212555549544327</v>
+        <v>0.2125555495443279</v>
       </c>
       <c r="D11">
-        <v>0.04590793275390773</v>
+        <v>0.04590793275390839</v>
       </c>
     </row>
     <row r="12">
@@ -543,13 +543,13 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.8792328439433735</v>
+        <v>-0.8792328439433733</v>
       </c>
       <c r="C12">
-        <v>0.2361583185844486</v>
+        <v>0.2361583185844496</v>
       </c>
       <c r="D12">
-        <v>0.1455604364008188</v>
+        <v>0.1455604364008195</v>
       </c>
     </row>
     <row r="13">
@@ -562,10 +562,10 @@
         <v>-0.9244434046616282</v>
       </c>
       <c r="C13">
-        <v>-0.2911616953380786</v>
+        <v>-0.2911616953380774</v>
       </c>
       <c r="D13">
-        <v>-0.03205483251718672</v>
+        <v>-0.03205483251718712</v>
       </c>
     </row>
     <row r="14">
@@ -575,13 +575,13 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.9444412008869187</v>
+        <v>-0.9444412008869186</v>
       </c>
       <c r="C14">
-        <v>0.2583902653651188</v>
+        <v>0.2583902653651199</v>
       </c>
       <c r="D14">
-        <v>0.07972264340073312</v>
+        <v>0.07972264340073353</v>
       </c>
     </row>
   </sheetData>
